--- a/data/nzd0597/nzd0597.xlsx
+++ b/data/nzd0597/nzd0597.xlsx
@@ -12092,9 +12092,15 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0317</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -12142,9 +12148,15 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0347</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -12192,9 +12204,15 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0292</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0341</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -12242,9 +12260,15 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0318</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -12292,9 +12316,15 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0353</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -12342,9 +12372,15 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0346</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0428</v>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -12392,9 +12428,15 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0674</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -12442,9 +12484,15 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.07530000000000001</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -12492,9 +12540,15 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0822</v>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -12542,9 +12596,15 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.081</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -12592,9 +12652,15 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0644</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.0901</v>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -12642,9 +12708,15 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1169</v>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -12692,9 +12764,15 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0762</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1459</v>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -12742,9 +12820,15 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1054</v>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -12792,9 +12876,15 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0772</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1497</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -12842,9 +12932,15 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1574</v>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -12892,9 +12988,15 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1052</v>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>

--- a/data/nzd0597/nzd0597.xlsx
+++ b/data/nzd0597/nzd0597.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S286"/>
+  <dimension ref="A1:S288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18409,10 +18409,10 @@
         <v>132.59</v>
       </c>
       <c r="J286" t="n">
-        <v>139</v>
+        <v>141.57</v>
       </c>
       <c r="K286" t="n">
-        <v>142.47</v>
+        <v>145.45</v>
       </c>
       <c r="L286" t="n">
         <v>154.59</v>
@@ -18436,6 +18436,132 @@
         <v>178.46</v>
       </c>
       <c r="S286" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:27:19+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>163.8</v>
+      </c>
+      <c r="C287" t="n">
+        <v>160.12</v>
+      </c>
+      <c r="D287" t="n">
+        <v>151.69</v>
+      </c>
+      <c r="E287" t="n">
+        <v>149.2</v>
+      </c>
+      <c r="F287" t="n">
+        <v>156.91</v>
+      </c>
+      <c r="G287" t="n">
+        <v>145.66</v>
+      </c>
+      <c r="H287" t="n">
+        <v>133.11</v>
+      </c>
+      <c r="I287" t="n">
+        <v>133.24</v>
+      </c>
+      <c r="J287" t="n">
+        <v>141.96</v>
+      </c>
+      <c r="K287" t="n">
+        <v>147.16</v>
+      </c>
+      <c r="L287" t="n">
+        <v>155.13</v>
+      </c>
+      <c r="M287" t="n">
+        <v>162.61</v>
+      </c>
+      <c r="N287" t="n">
+        <v>164.76</v>
+      </c>
+      <c r="O287" t="n">
+        <v>159.77</v>
+      </c>
+      <c r="P287" t="n">
+        <v>161.78</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>168.82</v>
+      </c>
+      <c r="R287" t="n">
+        <v>177.98</v>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>166.09</v>
+      </c>
+      <c r="C288" t="n">
+        <v>161.27</v>
+      </c>
+      <c r="D288" t="n">
+        <v>154.79</v>
+      </c>
+      <c r="E288" t="n">
+        <v>151.5</v>
+      </c>
+      <c r="F288" t="n">
+        <v>157.87</v>
+      </c>
+      <c r="G288" t="n">
+        <v>143.69</v>
+      </c>
+      <c r="H288" t="n">
+        <v>135.74</v>
+      </c>
+      <c r="I288" t="n">
+        <v>136.86</v>
+      </c>
+      <c r="J288" t="n">
+        <v>146.12</v>
+      </c>
+      <c r="K288" t="n">
+        <v>151.25</v>
+      </c>
+      <c r="L288" t="n">
+        <v>159.73</v>
+      </c>
+      <c r="M288" t="n">
+        <v>167.91</v>
+      </c>
+      <c r="N288" t="n">
+        <v>168.94</v>
+      </c>
+      <c r="O288" t="n">
+        <v>163.29</v>
+      </c>
+      <c r="P288" t="n">
+        <v>165.15</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>169.77</v>
+      </c>
+      <c r="R288" t="n">
+        <v>178.31</v>
+      </c>
+      <c r="S288" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -18452,7 +18578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B293"/>
+  <dimension ref="A1:B295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21385,6 +21511,26 @@
       </c>
       <c r="B293" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -21547,28 +21693,28 @@
         <v>0.0317</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8003557280543319</v>
+        <v>-0.7793149493268529</v>
       </c>
       <c r="J2" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K2" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1298575668753778</v>
+        <v>0.1248513111303443</v>
       </c>
       <c r="M2" t="n">
-        <v>12.5256111785872</v>
+        <v>12.54243752231587</v>
       </c>
       <c r="N2" t="n">
-        <v>232.7909348666397</v>
+        <v>232.760947798723</v>
       </c>
       <c r="O2" t="n">
-        <v>15.25748782947703</v>
+        <v>15.25650509778445</v>
       </c>
       <c r="P2" t="n">
-        <v>170.5752935721534</v>
+        <v>170.3603305966344</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21619,28 +21765,28 @@
         <v>0.0347</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8776905876555076</v>
+        <v>-0.8550793595972552</v>
       </c>
       <c r="J3" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K3" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1960062259833111</v>
+        <v>0.1885799621547948</v>
       </c>
       <c r="M3" t="n">
-        <v>10.89620271696265</v>
+        <v>10.92027046072159</v>
       </c>
       <c r="N3" t="n">
-        <v>171.3730649312749</v>
+        <v>172.011860859958</v>
       </c>
       <c r="O3" t="n">
-        <v>13.09095355317079</v>
+        <v>13.11532923185529</v>
       </c>
       <c r="P3" t="n">
-        <v>167.2013292153998</v>
+        <v>166.9703263829659</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21691,28 +21837,28 @@
         <v>0.0341</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5571657749293429</v>
+        <v>-0.5412769351353501</v>
       </c>
       <c r="J4" t="n">
+        <v>287</v>
+      </c>
+      <c r="K4" t="n">
         <v>285</v>
       </c>
-      <c r="K4" t="n">
-        <v>283</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.06203118644293915</v>
+        <v>0.05938913159364367</v>
       </c>
       <c r="M4" t="n">
-        <v>12.02813927216148</v>
+        <v>12.01216191181298</v>
       </c>
       <c r="N4" t="n">
-        <v>252.6204229951768</v>
+        <v>251.7611231377415</v>
       </c>
       <c r="O4" t="n">
-        <v>15.89403734093943</v>
+        <v>15.86698216857073</v>
       </c>
       <c r="P4" t="n">
-        <v>156.3380334392801</v>
+        <v>156.1746908381294</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21763,28 +21909,28 @@
         <v>0.0318</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.372993190212374</v>
+        <v>-0.3639974881631124</v>
       </c>
       <c r="J5" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K5" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04171625346231811</v>
+        <v>0.04032203947544644</v>
       </c>
       <c r="M5" t="n">
-        <v>10.56977915931469</v>
+        <v>10.53858295998742</v>
       </c>
       <c r="N5" t="n">
-        <v>173.3275081129451</v>
+        <v>172.4150480816324</v>
       </c>
       <c r="O5" t="n">
-        <v>13.16539054160358</v>
+        <v>13.13069107403081</v>
       </c>
       <c r="P5" t="n">
-        <v>153.5593685945749</v>
+        <v>153.4674593742226</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21835,28 +21981,28 @@
         <v>0.0353</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2781216923820146</v>
+        <v>-0.2619735638563271</v>
       </c>
       <c r="J6" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K6" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02951277056148383</v>
+        <v>0.02648572755361533</v>
       </c>
       <c r="M6" t="n">
-        <v>9.562283411350855</v>
+        <v>9.584801540903667</v>
       </c>
       <c r="N6" t="n">
-        <v>137.9515019043968</v>
+        <v>137.9242768434018</v>
       </c>
       <c r="O6" t="n">
-        <v>11.74527572704859</v>
+        <v>11.74411669064139</v>
       </c>
       <c r="P6" t="n">
-        <v>152.9449907441872</v>
+        <v>152.7800162972723</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21907,28 +22053,28 @@
         <v>0.0428</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2118272290885158</v>
+        <v>-0.2081516197409125</v>
       </c>
       <c r="J7" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K7" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01848958113465526</v>
+        <v>0.01812440036512764</v>
       </c>
       <c r="M7" t="n">
-        <v>9.275121427054993</v>
+        <v>9.227393324886906</v>
       </c>
       <c r="N7" t="n">
-        <v>129.1838652473966</v>
+        <v>128.3357855888255</v>
       </c>
       <c r="O7" t="n">
-        <v>11.36590802564391</v>
+        <v>11.32853854602726</v>
       </c>
       <c r="P7" t="n">
-        <v>147.5355563637166</v>
+        <v>147.4980129361692</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21979,28 +22125,28 @@
         <v>0.0674</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08646800949917836</v>
+        <v>-0.08731767816795573</v>
       </c>
       <c r="J8" t="n">
+        <v>287</v>
+      </c>
+      <c r="K8" t="n">
         <v>285</v>
       </c>
-      <c r="K8" t="n">
-        <v>283</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.00243654897014256</v>
+        <v>0.002522178588031831</v>
       </c>
       <c r="M8" t="n">
-        <v>10.45691512253025</v>
+        <v>10.39328655427651</v>
       </c>
       <c r="N8" t="n">
-        <v>164.7394427471695</v>
+        <v>163.5981464011123</v>
       </c>
       <c r="O8" t="n">
-        <v>12.83508639422304</v>
+        <v>12.79054910475357</v>
       </c>
       <c r="P8" t="n">
-        <v>137.2928534035209</v>
+        <v>137.3015782604647</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22051,28 +22197,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1797621361333503</v>
+        <v>-0.1878170966205319</v>
       </c>
       <c r="J9" t="n">
+        <v>287</v>
+      </c>
+      <c r="K9" t="n">
         <v>285</v>
       </c>
-      <c r="K9" t="n">
-        <v>283</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.0134435825344239</v>
+        <v>0.01484858275457379</v>
       </c>
       <c r="M9" t="n">
-        <v>9.168832172967434</v>
+        <v>9.146349848760943</v>
       </c>
       <c r="N9" t="n">
-        <v>127.6217317228123</v>
+        <v>126.9798574394477</v>
       </c>
       <c r="O9" t="n">
-        <v>11.29697887591246</v>
+        <v>11.2685339525356</v>
       </c>
       <c r="P9" t="n">
-        <v>145.5321268948236</v>
+        <v>145.6149159657703</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22123,28 +22269,28 @@
         <v>0.0822</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4319790550591008</v>
+        <v>-0.4296501574351629</v>
       </c>
       <c r="J10" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K10" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05985711886068301</v>
+        <v>0.06011040895653397</v>
       </c>
       <c r="M10" t="n">
-        <v>10.21920381651879</v>
+        <v>10.1538026701389</v>
       </c>
       <c r="N10" t="n">
-        <v>158.9572336660639</v>
+        <v>157.8165231813833</v>
       </c>
       <c r="O10" t="n">
-        <v>12.60782430342618</v>
+        <v>12.56250465398454</v>
       </c>
       <c r="P10" t="n">
-        <v>154.8946681198692</v>
+        <v>154.8708883459971</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22195,28 +22341,28 @@
         <v>0.081</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4005879291238547</v>
+        <v>-0.3990827019458201</v>
       </c>
       <c r="J11" t="n">
+        <v>287</v>
+      </c>
+      <c r="K11" t="n">
         <v>285</v>
       </c>
-      <c r="K11" t="n">
-        <v>283</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.05788569301539392</v>
+        <v>0.05833782372947305</v>
       </c>
       <c r="M11" t="n">
-        <v>9.505445770989985</v>
+        <v>9.442193302293731</v>
       </c>
       <c r="N11" t="n">
-        <v>140.5559917750339</v>
+        <v>139.4817274596976</v>
       </c>
       <c r="O11" t="n">
-        <v>11.85563122634278</v>
+        <v>11.81023824737239</v>
       </c>
       <c r="P11" t="n">
-        <v>160.0561347847392</v>
+        <v>160.0406788676272</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22267,28 +22413,28 @@
         <v>0.0901</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5123235949826805</v>
+        <v>-0.5085494992228077</v>
       </c>
       <c r="J12" t="n">
+        <v>287</v>
+      </c>
+      <c r="K12" t="n">
         <v>285</v>
       </c>
-      <c r="K12" t="n">
-        <v>283</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.07844622252409905</v>
+        <v>0.07843453003120593</v>
       </c>
       <c r="M12" t="n">
-        <v>10.60794177600217</v>
+        <v>10.55152352779318</v>
       </c>
       <c r="N12" t="n">
-        <v>165.9428895885911</v>
+        <v>164.8663276302302</v>
       </c>
       <c r="O12" t="n">
-        <v>12.88188222227602</v>
+        <v>12.84002833447926</v>
       </c>
       <c r="P12" t="n">
-        <v>168.0769486903414</v>
+        <v>168.0381358480815</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22339,28 +22485,28 @@
         <v>0.1169</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4764185781516623</v>
+        <v>-0.4694840328360808</v>
       </c>
       <c r="J13" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K13" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07832807551012588</v>
+        <v>0.07719597457795768</v>
       </c>
       <c r="M13" t="n">
-        <v>9.929936621373701</v>
+        <v>9.89581662532227</v>
       </c>
       <c r="N13" t="n">
-        <v>145.9762402521034</v>
+        <v>145.1823519886582</v>
       </c>
       <c r="O13" t="n">
-        <v>12.08206274822737</v>
+        <v>12.04916395392884</v>
       </c>
       <c r="P13" t="n">
-        <v>172.6299911511273</v>
+        <v>172.5595715793904</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22411,28 +22557,28 @@
         <v>0.1459</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5321828001465018</v>
+        <v>-0.5240403092224454</v>
       </c>
       <c r="J14" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K14" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1041394022896061</v>
+        <v>0.1024940046400209</v>
       </c>
       <c r="M14" t="n">
-        <v>9.266408008680072</v>
+        <v>9.247408479845308</v>
       </c>
       <c r="N14" t="n">
-        <v>132.1368307897577</v>
+        <v>131.4811966637145</v>
       </c>
       <c r="O14" t="n">
-        <v>11.49507854648056</v>
+        <v>11.46652504744635</v>
       </c>
       <c r="P14" t="n">
-        <v>174.831823625663</v>
+        <v>174.7486242318784</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -22483,28 +22629,28 @@
         <v>0.1054</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5841969005815245</v>
+        <v>-0.5794604353913088</v>
       </c>
       <c r="J15" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K15" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1256127365632314</v>
+        <v>0.1253975047733575</v>
       </c>
       <c r="M15" t="n">
-        <v>9.342027380988048</v>
+        <v>9.302763135652516</v>
       </c>
       <c r="N15" t="n">
-        <v>128.8443876259507</v>
+        <v>128.045628912073</v>
       </c>
       <c r="O15" t="n">
-        <v>11.35096417164422</v>
+        <v>11.31572485137709</v>
       </c>
       <c r="P15" t="n">
-        <v>173.3361328506111</v>
+        <v>173.2877320890983</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -22555,28 +22701,28 @@
         <v>0.1497</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4665553621222808</v>
+        <v>-0.4635043077918808</v>
       </c>
       <c r="J16" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K16" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1027302942500898</v>
+        <v>0.1028664575061868</v>
       </c>
       <c r="M16" t="n">
-        <v>8.08876804536318</v>
+        <v>8.049249528497358</v>
       </c>
       <c r="N16" t="n">
-        <v>103.1116427849025</v>
+        <v>102.4439283625972</v>
       </c>
       <c r="O16" t="n">
-        <v>10.154390320689</v>
+        <v>10.12145880605149</v>
       </c>
       <c r="P16" t="n">
-        <v>173.4205023878032</v>
+        <v>173.3893204989374</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -22627,28 +22773,28 @@
         <v>0.1574</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4686861821654411</v>
+        <v>-0.4663730305793705</v>
       </c>
       <c r="J17" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K17" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1612990404514399</v>
+        <v>0.1619611367488191</v>
       </c>
       <c r="M17" t="n">
-        <v>6.453119945737702</v>
+        <v>6.421303638433691</v>
       </c>
       <c r="N17" t="n">
-        <v>61.94646362047666</v>
+        <v>61.53405884273906</v>
       </c>
       <c r="O17" t="n">
-        <v>7.870607576323231</v>
+        <v>7.844364782615547</v>
       </c>
       <c r="P17" t="n">
-        <v>179.8398588993038</v>
+        <v>179.8162241101728</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -22699,28 +22845,28 @@
         <v>0.1052</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.364134664980461</v>
+        <v>-0.3649295435950512</v>
       </c>
       <c r="J18" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K18" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1161835703668753</v>
+        <v>0.1181941800169997</v>
       </c>
       <c r="M18" t="n">
-        <v>5.840471195378509</v>
+        <v>5.803394890957371</v>
       </c>
       <c r="N18" t="n">
-        <v>54.7038969097572</v>
+        <v>54.32381733730601</v>
       </c>
       <c r="O18" t="n">
-        <v>7.39620827923046</v>
+        <v>7.370469275243335</v>
       </c>
       <c r="P18" t="n">
-        <v>188.2186467539954</v>
+        <v>188.2267661296139</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -22758,7 +22904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S286"/>
+  <dimension ref="A1:S288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50370,12 +50516,12 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>-46.28420850256229,167.73247983920652</t>
+          <t>-46.28420697848941,167.73244661778568</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>-46.283441660558026,167.73242990198307</t>
+          <t>-46.283442313994435,167.73239130845408</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -50414,6 +50560,200 @@
         </is>
       </c>
       <c r="S286" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:27:19+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>-46.289932060660355,167.7314848704979</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>-46.28921987951745,167.73163126504002</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>-46.28851193926008,167.73183889116103</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>-46.28779881927834,167.73196991741492</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>-46.28707685854991,167.73196940927883</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>-46.286355455479,167.73218840441317</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>-46.285645930966744,167.73241908817323</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>-46.284928885934356,167.73248585344626</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>-46.28420674720902,167.73244157640298</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>-46.283442688946984,167.73236916250298</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>-46.28272611265081,167.7322407390582</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>-46.281956210132826,167.73207163925804</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>-46.28125467408723,167.73184581005663</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>-46.28052455828232,167.7316597839056</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>-46.279834577883705,167.73136990970596</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>-46.27915602962051,167.73101700566752</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>-46.2784825321109,167.73064265589085</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>-46.28993009582934,167.73145533640434</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>-46.2892188952334,167.73161643336465</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>-46.28850927961012,167.7317989115144</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>-46.287796846041005,167.73194025547252</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>-46.28707603694359,167.73195702852783</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>-46.286356623837314,167.73221387084507</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>-46.285644371256936,167.7323850902691</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>-46.28492673917386,167.73243905845692</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>-46.28420428020453,167.73238780165806</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>-46.28344358574583,167.7323161935325</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>-46.28272712123923,167.73218116593952</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>-46.28196532495526,167.73200425152933</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>-46.2812618626844,167.73179266342393</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>-46.28053264079809,167.73161570102982</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>-46.279842307187394,167.73132770255464</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>-46.27915820847486,167.73100510764922</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>-46.27848327334686,167.73063851705953</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0597/nzd0597.xlsx
+++ b/data/nzd0597/nzd0597.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S288"/>
+  <dimension ref="A1:S289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18567,6 +18567,69 @@
         </is>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>164.15</v>
+      </c>
+      <c r="C289" t="n">
+        <v>158.32</v>
+      </c>
+      <c r="D289" t="n">
+        <v>155.08</v>
+      </c>
+      <c r="E289" t="n">
+        <v>147.72</v>
+      </c>
+      <c r="F289" t="n">
+        <v>145.55</v>
+      </c>
+      <c r="G289" t="n">
+        <v>143</v>
+      </c>
+      <c r="H289" t="n">
+        <v>139.58</v>
+      </c>
+      <c r="I289" t="n">
+        <v>144.78</v>
+      </c>
+      <c r="J289" t="n">
+        <v>151.38</v>
+      </c>
+      <c r="K289" t="n">
+        <v>157.86</v>
+      </c>
+      <c r="L289" t="n">
+        <v>165.65</v>
+      </c>
+      <c r="M289" t="n">
+        <v>177.27</v>
+      </c>
+      <c r="N289" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="O289" t="n">
+        <v>174.44</v>
+      </c>
+      <c r="P289" t="n">
+        <v>173.34</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>175.74</v>
+      </c>
+      <c r="R289" t="n">
+        <v>182.03</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18578,7 +18641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B295"/>
+  <dimension ref="A1:B296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21531,6 +21594,16 @@
       </c>
       <c r="B295" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>-0.83</v>
       </c>
     </row>
   </sheetData>
@@ -21693,28 +21766,28 @@
         <v>0.0317</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7793149493268529</v>
+        <v>-0.7693863011901203</v>
       </c>
       <c r="J2" t="n">
+        <v>288</v>
+      </c>
+      <c r="K2" t="n">
         <v>287</v>
       </c>
-      <c r="K2" t="n">
-        <v>286</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1248513111303443</v>
+        <v>0.1225768284245532</v>
       </c>
       <c r="M2" t="n">
-        <v>12.54243752231587</v>
+        <v>12.5472424364953</v>
       </c>
       <c r="N2" t="n">
-        <v>232.760947798723</v>
+        <v>232.6516400976068</v>
       </c>
       <c r="O2" t="n">
-        <v>15.25650509778445</v>
+        <v>15.25292234614753</v>
       </c>
       <c r="P2" t="n">
-        <v>170.3603305966344</v>
+        <v>170.257947255301</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21765,28 +21838,28 @@
         <v>0.0347</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8550793595972552</v>
+        <v>-0.8454600722893597</v>
       </c>
       <c r="J3" t="n">
+        <v>288</v>
+      </c>
+      <c r="K3" t="n">
         <v>287</v>
       </c>
-      <c r="K3" t="n">
-        <v>286</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1885799621547948</v>
+        <v>0.1857233680369811</v>
       </c>
       <c r="M3" t="n">
-        <v>10.92027046072159</v>
+        <v>10.9250200423477</v>
       </c>
       <c r="N3" t="n">
-        <v>172.011860859958</v>
+        <v>172.0711756186028</v>
       </c>
       <c r="O3" t="n">
-        <v>13.11532923185529</v>
+        <v>13.11759031295774</v>
       </c>
       <c r="P3" t="n">
-        <v>166.9703263829659</v>
+        <v>166.8711331431345</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21837,28 +21910,28 @@
         <v>0.0341</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5412769351353501</v>
+        <v>-0.5320781189162433</v>
       </c>
       <c r="J4" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K4" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05938913159364367</v>
+        <v>0.05779243139619028</v>
       </c>
       <c r="M4" t="n">
-        <v>12.01216191181298</v>
+        <v>12.00885690589472</v>
       </c>
       <c r="N4" t="n">
-        <v>251.7611231377415</v>
+        <v>251.4768977586463</v>
       </c>
       <c r="O4" t="n">
-        <v>15.86698216857073</v>
+        <v>15.85802313526646</v>
       </c>
       <c r="P4" t="n">
-        <v>156.1746908381294</v>
+        <v>156.079248368225</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21909,28 +21982,28 @@
         <v>0.0318</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3639974881631124</v>
+        <v>-0.3613414282326049</v>
       </c>
       <c r="J5" t="n">
+        <v>288</v>
+      </c>
+      <c r="K5" t="n">
         <v>287</v>
       </c>
-      <c r="K5" t="n">
-        <v>286</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.04032203947544644</v>
+        <v>0.04004220056488206</v>
       </c>
       <c r="M5" t="n">
-        <v>10.53858295998742</v>
+        <v>10.51444769185561</v>
       </c>
       <c r="N5" t="n">
-        <v>172.4150480816324</v>
+        <v>171.8645157805401</v>
       </c>
       <c r="O5" t="n">
-        <v>13.13069107403081</v>
+        <v>13.10971074358775</v>
       </c>
       <c r="P5" t="n">
-        <v>153.4674593742226</v>
+        <v>153.4400703191647</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21981,28 +22054,28 @@
         <v>0.0353</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2619735638563271</v>
+        <v>-0.2622146150548553</v>
       </c>
       <c r="J6" t="n">
+        <v>288</v>
+      </c>
+      <c r="K6" t="n">
         <v>287</v>
       </c>
-      <c r="K6" t="n">
-        <v>286</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02648572755361533</v>
+        <v>0.0267323068475056</v>
       </c>
       <c r="M6" t="n">
-        <v>9.584801540903667</v>
+        <v>9.552464171381237</v>
       </c>
       <c r="N6" t="n">
-        <v>137.9242768434018</v>
+        <v>137.4441180626418</v>
       </c>
       <c r="O6" t="n">
-        <v>11.74411669064139</v>
+        <v>11.72365634359187</v>
       </c>
       <c r="P6" t="n">
-        <v>152.7800162972723</v>
+        <v>152.7825019959091</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22053,28 +22126,28 @@
         <v>0.0428</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2081516197409125</v>
+        <v>-0.2074761198833743</v>
       </c>
       <c r="J7" t="n">
+        <v>288</v>
+      </c>
+      <c r="K7" t="n">
         <v>287</v>
       </c>
-      <c r="K7" t="n">
-        <v>286</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01812440036512764</v>
+        <v>0.01814500734088764</v>
       </c>
       <c r="M7" t="n">
-        <v>9.227393324886906</v>
+        <v>9.198324835979678</v>
       </c>
       <c r="N7" t="n">
-        <v>128.3357855888255</v>
+        <v>127.8918706437867</v>
       </c>
       <c r="O7" t="n">
-        <v>11.32853854602726</v>
+        <v>11.30892880178254</v>
       </c>
       <c r="P7" t="n">
-        <v>147.4980129361692</v>
+        <v>147.4910472413906</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22125,28 +22198,28 @@
         <v>0.0674</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08731767816795573</v>
+        <v>-0.0841107292768748</v>
       </c>
       <c r="J8" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K8" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002522178588031831</v>
+        <v>0.002357757562685858</v>
       </c>
       <c r="M8" t="n">
-        <v>10.39328655427651</v>
+        <v>10.3709146356959</v>
       </c>
       <c r="N8" t="n">
-        <v>163.5981464011123</v>
+        <v>163.0985699923849</v>
       </c>
       <c r="O8" t="n">
-        <v>12.79054910475357</v>
+        <v>12.77100505020591</v>
       </c>
       <c r="P8" t="n">
-        <v>137.3015782604647</v>
+        <v>137.2683045091763</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22197,28 +22270,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1878170966205319</v>
+        <v>-0.1849421447965851</v>
       </c>
       <c r="J9" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K9" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01484858275457379</v>
+        <v>0.01450719558177049</v>
       </c>
       <c r="M9" t="n">
-        <v>9.146349848760943</v>
+        <v>9.127964678109242</v>
       </c>
       <c r="N9" t="n">
-        <v>126.9798574394477</v>
+        <v>126.5940937704619</v>
       </c>
       <c r="O9" t="n">
-        <v>11.2685339525356</v>
+        <v>11.25140407995651</v>
       </c>
       <c r="P9" t="n">
-        <v>145.6149159657703</v>
+        <v>145.5850868555459</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22269,28 +22342,28 @@
         <v>0.0822</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4296501574351629</v>
+        <v>-0.4242193978015982</v>
       </c>
       <c r="J10" t="n">
+        <v>288</v>
+      </c>
+      <c r="K10" t="n">
         <v>287</v>
       </c>
-      <c r="K10" t="n">
-        <v>286</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.06011040895653397</v>
+        <v>0.05904081670955597</v>
       </c>
       <c r="M10" t="n">
-        <v>10.1538026701389</v>
+        <v>10.14630238231065</v>
       </c>
       <c r="N10" t="n">
-        <v>157.8165231813833</v>
+        <v>157.4765802862423</v>
       </c>
       <c r="O10" t="n">
-        <v>12.56250465398454</v>
+        <v>12.54896729959252</v>
       </c>
       <c r="P10" t="n">
-        <v>154.8708883459971</v>
+        <v>154.8148868330413</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22341,28 +22414,28 @@
         <v>0.081</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3990827019458201</v>
+        <v>-0.3932631173199707</v>
       </c>
       <c r="J11" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K11" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05833782372947305</v>
+        <v>0.05706613048285281</v>
       </c>
       <c r="M11" t="n">
-        <v>9.442193302293731</v>
+        <v>9.436296068310776</v>
       </c>
       <c r="N11" t="n">
-        <v>139.4817274596976</v>
+        <v>139.2325952542265</v>
       </c>
       <c r="O11" t="n">
-        <v>11.81023824737239</v>
+        <v>11.79968623541434</v>
       </c>
       <c r="P11" t="n">
-        <v>160.0406788676272</v>
+        <v>159.9802976710385</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22413,28 +22486,28 @@
         <v>0.0901</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5085494992228077</v>
+        <v>-0.5008609214818186</v>
       </c>
       <c r="J12" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K12" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07843453003120593</v>
+        <v>0.07662556060985248</v>
       </c>
       <c r="M12" t="n">
-        <v>10.55152352779318</v>
+        <v>10.55148621000247</v>
       </c>
       <c r="N12" t="n">
-        <v>164.8663276302302</v>
+        <v>164.7062778178593</v>
       </c>
       <c r="O12" t="n">
-        <v>12.84002833447926</v>
+        <v>12.83379436557479</v>
       </c>
       <c r="P12" t="n">
-        <v>168.0381358480815</v>
+        <v>167.9583628824984</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22485,28 +22558,28 @@
         <v>0.1169</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4694840328360808</v>
+        <v>-0.4577056987486705</v>
       </c>
       <c r="J13" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K13" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07719597457795768</v>
+        <v>0.07370669712723932</v>
       </c>
       <c r="M13" t="n">
-        <v>9.89581662532227</v>
+        <v>9.919543515686396</v>
       </c>
       <c r="N13" t="n">
-        <v>145.1823519886582</v>
+        <v>145.6762192562053</v>
       </c>
       <c r="O13" t="n">
-        <v>12.04916395392884</v>
+        <v>12.06964039465159</v>
       </c>
       <c r="P13" t="n">
-        <v>172.5595715793904</v>
+        <v>172.4388680209541</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22557,28 +22630,28 @@
         <v>0.1459</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5240403092224454</v>
+        <v>-0.5133225358348741</v>
       </c>
       <c r="J14" t="n">
+        <v>288</v>
+      </c>
+      <c r="K14" t="n">
         <v>287</v>
       </c>
-      <c r="K14" t="n">
-        <v>286</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.1024940046400209</v>
+        <v>0.09888444206157443</v>
       </c>
       <c r="M14" t="n">
-        <v>9.247408479845308</v>
+        <v>9.274028253103255</v>
       </c>
       <c r="N14" t="n">
-        <v>131.4811966637145</v>
+        <v>131.8407554374391</v>
       </c>
       <c r="O14" t="n">
-        <v>11.46652504744635</v>
+        <v>11.48219297161649</v>
       </c>
       <c r="P14" t="n">
-        <v>174.7486242318784</v>
+        <v>174.6381035007614</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -22629,28 +22702,28 @@
         <v>0.1054</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5794604353913088</v>
+        <v>-0.5680653482929706</v>
       </c>
       <c r="J15" t="n">
+        <v>288</v>
+      </c>
+      <c r="K15" t="n">
         <v>287</v>
       </c>
-      <c r="K15" t="n">
-        <v>286</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1253975047733575</v>
+        <v>0.1211551424212737</v>
       </c>
       <c r="M15" t="n">
-        <v>9.302763135652516</v>
+        <v>9.331617023679744</v>
       </c>
       <c r="N15" t="n">
-        <v>128.045628912073</v>
+        <v>128.5237712100172</v>
       </c>
       <c r="O15" t="n">
-        <v>11.31572485137709</v>
+        <v>11.33683250339429</v>
       </c>
       <c r="P15" t="n">
-        <v>173.2877320890983</v>
+        <v>173.1702269589088</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -22701,28 +22774,28 @@
         <v>0.1497</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4635043077918808</v>
+        <v>-0.4550600543459268</v>
       </c>
       <c r="J16" t="n">
+        <v>288</v>
+      </c>
+      <c r="K16" t="n">
         <v>287</v>
       </c>
-      <c r="K16" t="n">
-        <v>286</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1028664575061868</v>
+        <v>0.09976651244118406</v>
       </c>
       <c r="M16" t="n">
-        <v>8.049249528497358</v>
+        <v>8.067374725869202</v>
       </c>
       <c r="N16" t="n">
-        <v>102.4439283625972</v>
+        <v>102.5945526980401</v>
       </c>
       <c r="O16" t="n">
-        <v>10.12145880605149</v>
+        <v>10.12889691417778</v>
       </c>
       <c r="P16" t="n">
-        <v>173.3893204989374</v>
+        <v>173.3022441043511</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -22773,28 +22846,28 @@
         <v>0.1574</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4663730305793705</v>
+        <v>-0.4606793762617763</v>
       </c>
       <c r="J17" t="n">
+        <v>288</v>
+      </c>
+      <c r="K17" t="n">
         <v>287</v>
       </c>
-      <c r="K17" t="n">
-        <v>286</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.1619611367488191</v>
+        <v>0.1591792617675905</v>
       </c>
       <c r="M17" t="n">
-        <v>6.421303638433691</v>
+        <v>6.4315855135784</v>
       </c>
       <c r="N17" t="n">
-        <v>61.53405884273906</v>
+        <v>61.55041267414828</v>
       </c>
       <c r="O17" t="n">
-        <v>7.844364782615547</v>
+        <v>7.845407106973371</v>
       </c>
       <c r="P17" t="n">
-        <v>179.8162241101728</v>
+        <v>179.75751165049</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -22845,28 +22918,28 @@
         <v>0.1052</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3649295435950512</v>
+        <v>-0.3625662562134213</v>
       </c>
       <c r="J18" t="n">
+        <v>288</v>
+      </c>
+      <c r="K18" t="n">
         <v>287</v>
       </c>
-      <c r="K18" t="n">
-        <v>286</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1181941800169997</v>
+        <v>0.1175656438830497</v>
       </c>
       <c r="M18" t="n">
-        <v>5.803394890957371</v>
+        <v>5.795612926298328</v>
       </c>
       <c r="N18" t="n">
-        <v>54.32381733730601</v>
+        <v>54.17429223575336</v>
       </c>
       <c r="O18" t="n">
-        <v>7.370469275243335</v>
+        <v>7.360318759113179</v>
       </c>
       <c r="P18" t="n">
-        <v>188.2267661296139</v>
+        <v>188.2023961191824</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -22904,7 +22977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S288"/>
+  <dimension ref="A1:S289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50759,6 +50832,103 @@
         </is>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>-46.28993176035917,167.73148035655328</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>-46.28922142013208,167.7316544798377</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>-46.28850903080343,167.7317951714832</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>-46.28780008900965,167.7319890042315</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>-46.28708658079036,167.73211591486964</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>-46.28635703305791,167.7322227905602</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>-46.28564209394394,167.7323354507487</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>-46.28492204232746,167.7323366782779</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>-46.284201160831024,167.73231980763975</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>-46.28344503504327,167.7322305884246</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>-46.28272841920268,167.73210449792674</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>-46.28198142197593,167.7318852422109</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>-46.28127465763664,167.73169806747413</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>-46.280558242968944,167.73147606343463</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>-46.279861091392256,167.7312251278606</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>-46.27917190082492,167.73093033797807</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>-46.2784916290868,167.73059186113613</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0597/nzd0597.xlsx
+++ b/data/nzd0597/nzd0597.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S289"/>
+  <dimension ref="A1:S291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18630,6 +18630,132 @@
         </is>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:26:29+00:00</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>174.76</v>
+      </c>
+      <c r="C290" t="n">
+        <v>167.01</v>
+      </c>
+      <c r="D290" t="n">
+        <v>163.26</v>
+      </c>
+      <c r="E290" t="n">
+        <v>157.17</v>
+      </c>
+      <c r="F290" t="n">
+        <v>158.71</v>
+      </c>
+      <c r="G290" t="n">
+        <v>155.26</v>
+      </c>
+      <c r="H290" t="n">
+        <v>150.63</v>
+      </c>
+      <c r="I290" t="n">
+        <v>158.08</v>
+      </c>
+      <c r="J290" t="n">
+        <v>165.02</v>
+      </c>
+      <c r="K290" t="n">
+        <v>171.14</v>
+      </c>
+      <c r="L290" t="n">
+        <v>174.45</v>
+      </c>
+      <c r="M290" t="n">
+        <v>181.84</v>
+      </c>
+      <c r="N290" t="n">
+        <v>173.74</v>
+      </c>
+      <c r="O290" t="n">
+        <v>175.66</v>
+      </c>
+      <c r="P290" t="n">
+        <v>175.31</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>176.06</v>
+      </c>
+      <c r="R290" t="n">
+        <v>183.02</v>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-22 22:26:04+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>174.76</v>
+      </c>
+      <c r="C291" t="n">
+        <v>167.01</v>
+      </c>
+      <c r="D291" t="n">
+        <v>163.26</v>
+      </c>
+      <c r="E291" t="n">
+        <v>157.17</v>
+      </c>
+      <c r="F291" t="n">
+        <v>158.71</v>
+      </c>
+      <c r="G291" t="n">
+        <v>155.26</v>
+      </c>
+      <c r="H291" t="n">
+        <v>150.63</v>
+      </c>
+      <c r="I291" t="n">
+        <v>158.08</v>
+      </c>
+      <c r="J291" t="n">
+        <v>165.02</v>
+      </c>
+      <c r="K291" t="n">
+        <v>171.14</v>
+      </c>
+      <c r="L291" t="n">
+        <v>174.45</v>
+      </c>
+      <c r="M291" t="n">
+        <v>181.84</v>
+      </c>
+      <c r="N291" t="n">
+        <v>167.97</v>
+      </c>
+      <c r="O291" t="n">
+        <v>175.66</v>
+      </c>
+      <c r="P291" t="n">
+        <v>175.31</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>172.47</v>
+      </c>
+      <c r="R291" t="n">
+        <v>180.1</v>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18641,7 +18767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B296"/>
+  <dimension ref="A1:B298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21604,6 +21730,26 @@
       </c>
       <c r="B296" t="n">
         <v>-0.83</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-05-22 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>
@@ -21766,28 +21912,28 @@
         <v>0.0317</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7693863011901203</v>
+        <v>-0.7349316961793776</v>
       </c>
       <c r="J2" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K2" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1225768284245532</v>
+        <v>0.1128186258265659</v>
       </c>
       <c r="M2" t="n">
-        <v>12.5472424364953</v>
+        <v>12.62678335343492</v>
       </c>
       <c r="N2" t="n">
-        <v>232.6516400976068</v>
+        <v>235.2292893550152</v>
       </c>
       <c r="O2" t="n">
-        <v>15.25292234614753</v>
+        <v>15.3371864875868</v>
       </c>
       <c r="P2" t="n">
-        <v>170.257947255301</v>
+        <v>169.8996057838029</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21838,28 +21984,28 @@
         <v>0.0347</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8454600722893597</v>
+        <v>-0.8142555259961215</v>
       </c>
       <c r="J3" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K3" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1857233680369811</v>
+        <v>0.1739942389392309</v>
       </c>
       <c r="M3" t="n">
-        <v>10.9250200423477</v>
+        <v>10.98850589681171</v>
       </c>
       <c r="N3" t="n">
-        <v>172.0711756186028</v>
+        <v>174.3152838009689</v>
       </c>
       <c r="O3" t="n">
-        <v>13.11759031295774</v>
+        <v>13.20285135116536</v>
       </c>
       <c r="P3" t="n">
-        <v>166.8711331431345</v>
+        <v>166.5465933851152</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21910,28 +22056,28 @@
         <v>0.0341</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5320781189162433</v>
+        <v>-0.5024189847749654</v>
       </c>
       <c r="J4" t="n">
+        <v>290</v>
+      </c>
+      <c r="K4" t="n">
         <v>288</v>
       </c>
-      <c r="K4" t="n">
-        <v>286</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.05779243139619028</v>
+        <v>0.05202133390543073</v>
       </c>
       <c r="M4" t="n">
-        <v>12.00885690589472</v>
+        <v>12.04827397005271</v>
       </c>
       <c r="N4" t="n">
-        <v>251.4768977586463</v>
+        <v>252.8010846467037</v>
       </c>
       <c r="O4" t="n">
-        <v>15.85802313526646</v>
+        <v>15.89971964050636</v>
       </c>
       <c r="P4" t="n">
-        <v>156.079248368225</v>
+        <v>155.7688935975922</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21982,28 +22128,28 @@
         <v>0.0318</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3613414282326049</v>
+        <v>-0.3429264859616765</v>
       </c>
       <c r="J5" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K5" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04004220056488206</v>
+        <v>0.036509973706636</v>
       </c>
       <c r="M5" t="n">
-        <v>10.51444769185561</v>
+        <v>10.52928285803026</v>
       </c>
       <c r="N5" t="n">
-        <v>171.8645157805401</v>
+        <v>171.8713910709247</v>
       </c>
       <c r="O5" t="n">
-        <v>13.10971074358775</v>
+        <v>13.10997296224995</v>
       </c>
       <c r="P5" t="n">
-        <v>153.4400703191647</v>
+        <v>153.2485477215328</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22054,28 +22200,28 @@
         <v>0.0353</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2622146150548553</v>
+        <v>-0.2443943355854952</v>
       </c>
       <c r="J6" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K6" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0267323068475056</v>
+        <v>0.02347319566785044</v>
       </c>
       <c r="M6" t="n">
-        <v>9.552464171381237</v>
+        <v>9.584298360221144</v>
       </c>
       <c r="N6" t="n">
-        <v>137.4441180626418</v>
+        <v>137.6131866882497</v>
       </c>
       <c r="O6" t="n">
-        <v>11.72365634359187</v>
+        <v>11.73086470334773</v>
       </c>
       <c r="P6" t="n">
-        <v>152.7825019959091</v>
+        <v>152.597164228646</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22126,28 +22272,28 @@
         <v>0.0428</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2074761198833743</v>
+        <v>-0.1891130200111927</v>
       </c>
       <c r="J7" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K7" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01814500734088764</v>
+        <v>0.01521508824115259</v>
       </c>
       <c r="M7" t="n">
-        <v>9.198324835979678</v>
+        <v>9.219104020849501</v>
       </c>
       <c r="N7" t="n">
-        <v>127.8918706437867</v>
+        <v>128.1963326025706</v>
       </c>
       <c r="O7" t="n">
-        <v>11.30892880178254</v>
+        <v>11.32238193149174</v>
       </c>
       <c r="P7" t="n">
-        <v>147.4910472413906</v>
+        <v>147.3000640081104</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22198,28 +22344,28 @@
         <v>0.0674</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0841107292768748</v>
+        <v>-0.06237527891543128</v>
       </c>
       <c r="J8" t="n">
+        <v>290</v>
+      </c>
+      <c r="K8" t="n">
         <v>288</v>
       </c>
-      <c r="K8" t="n">
-        <v>286</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.002357757562685858</v>
+        <v>0.00130516201246933</v>
       </c>
       <c r="M8" t="n">
-        <v>10.3709146356959</v>
+        <v>10.39118725879519</v>
       </c>
       <c r="N8" t="n">
-        <v>163.0985699923849</v>
+        <v>163.6150130568997</v>
       </c>
       <c r="O8" t="n">
-        <v>12.77100505020591</v>
+        <v>12.79120842832684</v>
       </c>
       <c r="P8" t="n">
-        <v>137.2683045091763</v>
+        <v>137.0408639598969</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22270,28 +22416,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1849421447965851</v>
+        <v>-0.1606861627279961</v>
       </c>
       <c r="J9" t="n">
+        <v>290</v>
+      </c>
+      <c r="K9" t="n">
         <v>288</v>
       </c>
-      <c r="K9" t="n">
-        <v>286</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01450719558177049</v>
+        <v>0.01098412800875626</v>
       </c>
       <c r="M9" t="n">
-        <v>9.127964678109242</v>
+        <v>9.178802990061184</v>
       </c>
       <c r="N9" t="n">
-        <v>126.5940937704619</v>
+        <v>127.7686791290219</v>
       </c>
       <c r="O9" t="n">
-        <v>11.25140407995651</v>
+        <v>11.30348084127283</v>
       </c>
       <c r="P9" t="n">
-        <v>145.5850868555459</v>
+        <v>145.3312712601297</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22342,28 +22488,28 @@
         <v>0.0822</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4242193978015982</v>
+        <v>-0.3945223492267224</v>
       </c>
       <c r="J10" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K10" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05904081670955597</v>
+        <v>0.05127376016901419</v>
       </c>
       <c r="M10" t="n">
-        <v>10.14630238231065</v>
+        <v>10.22718106049777</v>
       </c>
       <c r="N10" t="n">
-        <v>157.4765802862423</v>
+        <v>159.4978364339157</v>
       </c>
       <c r="O10" t="n">
-        <v>12.54896729959252</v>
+        <v>12.62924528362308</v>
       </c>
       <c r="P10" t="n">
-        <v>154.8148868330413</v>
+        <v>154.5060261098245</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22414,28 +22560,28 @@
         <v>0.081</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3932631173199707</v>
+        <v>-0.3631701990445362</v>
       </c>
       <c r="J11" t="n">
+        <v>290</v>
+      </c>
+      <c r="K11" t="n">
         <v>288</v>
       </c>
-      <c r="K11" t="n">
-        <v>286</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.05706613048285281</v>
+        <v>0.04875413325811195</v>
       </c>
       <c r="M11" t="n">
-        <v>9.436296068310776</v>
+        <v>9.513593317195292</v>
       </c>
       <c r="N11" t="n">
-        <v>139.2325952542265</v>
+        <v>141.426736755804</v>
       </c>
       <c r="O11" t="n">
-        <v>11.79968623541434</v>
+        <v>11.89229737081124</v>
       </c>
       <c r="P11" t="n">
-        <v>159.9802976710385</v>
+        <v>159.6654039369547</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22486,28 +22632,28 @@
         <v>0.0901</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5008609214818186</v>
+        <v>-0.4733129450890591</v>
       </c>
       <c r="J12" t="n">
+        <v>290</v>
+      </c>
+      <c r="K12" t="n">
         <v>288</v>
       </c>
-      <c r="K12" t="n">
-        <v>286</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.07662556060985248</v>
+        <v>0.06896541667405154</v>
       </c>
       <c r="M12" t="n">
-        <v>10.55148621000247</v>
+        <v>10.60882711112677</v>
       </c>
       <c r="N12" t="n">
-        <v>164.7062778178593</v>
+        <v>166.2114674165556</v>
       </c>
       <c r="O12" t="n">
-        <v>12.83379436557479</v>
+        <v>12.89230264214099</v>
       </c>
       <c r="P12" t="n">
-        <v>167.9583628824984</v>
+        <v>167.6700993717562</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22558,28 +22704,28 @@
         <v>0.1169</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4577056987486705</v>
+        <v>-0.4281046262525983</v>
       </c>
       <c r="J13" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K13" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07370669712723932</v>
+        <v>0.0647278864050691</v>
       </c>
       <c r="M13" t="n">
-        <v>9.919543515686396</v>
+        <v>9.995275594320864</v>
       </c>
       <c r="N13" t="n">
-        <v>145.6762192562053</v>
+        <v>147.7954979183663</v>
       </c>
       <c r="O13" t="n">
-        <v>12.06964039465159</v>
+        <v>12.15711717136782</v>
       </c>
       <c r="P13" t="n">
-        <v>172.4388680209541</v>
+        <v>172.132900989001</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22630,28 +22776,28 @@
         <v>0.1459</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5133225358348741</v>
+        <v>-0.4997498701273109</v>
       </c>
       <c r="J14" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K14" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09888444206157443</v>
+        <v>0.09508327684150508</v>
       </c>
       <c r="M14" t="n">
-        <v>9.274028253103255</v>
+        <v>9.284390682365807</v>
       </c>
       <c r="N14" t="n">
-        <v>131.8407554374391</v>
+        <v>131.6363052820896</v>
       </c>
       <c r="O14" t="n">
-        <v>11.48219297161649</v>
+        <v>11.47328659461139</v>
       </c>
       <c r="P14" t="n">
-        <v>174.6381035007614</v>
+        <v>174.4970209920316</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -22702,28 +22848,28 @@
         <v>0.1054</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5680653482929706</v>
+        <v>-0.5437871886869526</v>
       </c>
       <c r="J15" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K15" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1211551424212737</v>
+        <v>0.1120992384615244</v>
       </c>
       <c r="M15" t="n">
-        <v>9.331617023679744</v>
+        <v>9.394524680963935</v>
       </c>
       <c r="N15" t="n">
-        <v>128.5237712100172</v>
+        <v>129.7136081581437</v>
       </c>
       <c r="O15" t="n">
-        <v>11.33683250339429</v>
+        <v>11.38918821330755</v>
       </c>
       <c r="P15" t="n">
-        <v>173.1702269589088</v>
+        <v>172.9177244993399</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -22774,28 +22920,28 @@
         <v>0.1497</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4550600543459268</v>
+        <v>-0.4355869320802928</v>
       </c>
       <c r="J16" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K16" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09976651244118406</v>
+        <v>0.09239319883947394</v>
       </c>
       <c r="M16" t="n">
-        <v>8.067374725869202</v>
+        <v>8.11871451600603</v>
       </c>
       <c r="N16" t="n">
-        <v>102.5945526980401</v>
+        <v>103.2222336977032</v>
       </c>
       <c r="O16" t="n">
-        <v>10.12889691417778</v>
+        <v>10.15983433416624</v>
       </c>
       <c r="P16" t="n">
-        <v>173.3022441043511</v>
+        <v>173.0997159337404</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -22846,28 +22992,28 @@
         <v>0.1574</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4606793762617763</v>
+        <v>-0.4514019903170784</v>
       </c>
       <c r="J17" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K17" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1591792617675905</v>
+        <v>0.1551483130228856</v>
       </c>
       <c r="M17" t="n">
-        <v>6.4315855135784</v>
+        <v>6.439424294423826</v>
       </c>
       <c r="N17" t="n">
-        <v>61.55041267414828</v>
+        <v>61.45060848256191</v>
       </c>
       <c r="O17" t="n">
-        <v>7.845407106973371</v>
+        <v>7.839043850021628</v>
       </c>
       <c r="P17" t="n">
-        <v>179.75751165049</v>
+        <v>179.661072062866</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -22918,28 +23064,28 @@
         <v>0.1052</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3625662562134213</v>
+        <v>-0.3584722375527554</v>
       </c>
       <c r="J18" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K18" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1175656438830497</v>
+        <v>0.1166861890386839</v>
       </c>
       <c r="M18" t="n">
-        <v>5.795612926298328</v>
+        <v>5.776529071721948</v>
       </c>
       <c r="N18" t="n">
-        <v>54.17429223575336</v>
+        <v>53.87315978335264</v>
       </c>
       <c r="O18" t="n">
-        <v>7.360318759113179</v>
+        <v>7.339833770825647</v>
       </c>
       <c r="P18" t="n">
-        <v>188.2023961191824</v>
+        <v>188.1598563006206</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -22977,7 +23123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S289"/>
+  <dimension ref="A1:S291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50929,6 +51075,200 @@
         </is>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:26:29+00:00</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>-46.28992265685902,167.7313435195776</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>-46.28921398234368,167.73154240396926</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>-46.28850201268929,167.73168967682852</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>-46.28779198154938,167.7318671323482</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>-46.28707531803697,167.73194619537108</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>-46.28634976187545,167.7320643040569</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>-46.285635540618806,167.73219260789165</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>-46.28491415474108,167.73216475202474</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>-46.284193071621644,167.73214348860301</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>-46.28344794659858,167.73205860116127</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>-46.28273034851212,167.7319905319634</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>-46.28198928126559,167.7318271361438</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>-46.2812701175015,167.7317316337832</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>-46.28056104427198,167.73146078469514</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>-46.279865609678815,167.73120045481738</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>-46.27917263475181,167.73092633022256</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>-46.27849385278848,167.73057944463827</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-22 22:26:04+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>-46.28992265685902,167.7313435195776</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>-46.28921398234368,167.73154240396926</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>-46.28850201268929,167.73168967682852</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>-46.28779198154938,167.7318671323482</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>-46.28707531803697,167.73194619537108</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>-46.28634976187545,167.7320643040569</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>-46.285635540618806,167.73219260789165</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>-46.28491415474108,167.73216475202474</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>-46.284193071621644,167.73214348860301</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>-46.28344794659858,167.73205860116127</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>-46.28273034851212,167.7319905319634</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>-46.28198928126559,167.7318271361438</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>-46.281260194519376,167.73180499649527</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>-46.28056104427198,167.73146078469514</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>-46.279865609678815,167.73120045481738</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>-46.27916440100129,167.73097129222418</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>-46.27848729398762,167.73061606703345</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
